--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:13</t>
+    <t xml:space="preserve">2026-10-05 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1120792.12</v>
+        <v>1120792.13</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>998303.12</v>
+        <v>998303.13</v>
       </c>
     </row>
     <row r="5">
@@ -636,7 +636,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>965026.62</v>
+        <v>965026.63</v>
       </c>
     </row>
     <row r="7">
@@ -721,7 +721,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>930455.12</v>
+        <v>930455.13</v>
       </c>
     </row>
     <row r="12">
@@ -806,7 +806,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>874080.62</v>
+        <v>874080.63</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>864528.62</v>
+        <v>864528.63</v>
       </c>
     </row>
     <row r="19">
@@ -891,7 +891,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>841396.12</v>
+        <v>841396.13</v>
       </c>
     </row>
     <row r="22">
@@ -959,7 +959,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>790569.62</v>
+        <v>790569.63</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>780185.62</v>
+        <v>780185.63</v>
       </c>
     </row>
     <row r="27">
@@ -1027,7 +1027,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>755253.12</v>
+        <v>755253.13</v>
       </c>
     </row>
     <row r="30">
@@ -1061,7 +1061,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>717648.62</v>
+        <v>717648.63</v>
       </c>
     </row>
   </sheetData>
